--- a/eval_output/廠務部_陳家祥_評分表.xlsx
+++ b/eval_output/廠務部_陳家祥_評分表.xlsx
@@ -1337,6 +1337,11 @@
           <t>劉祐誠</t>
         </is>
       </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>鍾欣芳</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="36" t="inlineStr">

--- a/eval_output/廠務部_陳家祥_評分表.xlsx
+++ b/eval_output/廠務部_陳家祥_評分表.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="行政部內共評" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="跨部門共評" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,15 +59,8 @@
       <b val="1"/>
       <sz val="18"/>
     </font>
-    <font>
-      <name val="微軟正黑體"/>
-      <charset val="136"/>
-      <family val="2"/>
-      <color rgb="FFFF0000"/>
-      <sz val="12"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -105,26 +97,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.3999755851924192"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -211,20 +185,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -328,54 +293,6 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
       <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1163,395 +1080,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AK19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="23.54296875" customWidth="1" min="1" max="1"/>
-    <col width="57.36328125" customWidth="1" min="2" max="2"/>
-    <col width="42.7265625" customWidth="1" min="3" max="3"/>
-    <col width="11.08984375" customWidth="1" min="4" max="4"/>
-    <col width="8.7265625" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="16" customHeight="1">
-      <c r="A1" s="34" t="inlineStr">
-        <is>
-          <t>樂聯工業股份有限公司</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="35" t="inlineStr">
-        <is>
-          <t>2025年度 年終 績效考核跨部門共同評分表(非主管職)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>部門/單位</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>評分者</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>受評人數</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="49" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>廠務部</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>陳家祥</t>
-        </is>
-      </c>
-      <c r="C5" s="3">
-        <f>COUNTIF(D6:P6,"&lt;&gt;")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="30.5" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>受評者姓名</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>白惇維</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>王柳琦</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>徐惠蘭</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>沙洋</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>朱冠瑋</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>周清家</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>詹郁瑛</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>林依婷</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>王秀雯</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>石容瑄</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>陳惠萍</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>尤念萍</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>林德和</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>羅文彥</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>楊心恬</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>陳巧倫</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>郭惠婷</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>尤秐棠</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>陳孟怡</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>劉祐誠</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>鍾欣芳</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="36" t="inlineStr">
-        <is>
-          <t>占比</t>
-        </is>
-      </c>
-      <c r="B7" s="36" t="inlineStr">
-        <is>
-          <t>題目</t>
-        </is>
-      </c>
-      <c r="C7" s="36" t="inlineStr">
-        <is>
-          <t>評分方式</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="33.5" customHeight="1">
-      <c r="A8" s="37" t="inlineStr">
-        <is>
-          <t>工作知識20%</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>公司辦法考核</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>根據考核固定成績</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="123" customHeight="1">
-      <c r="A9" s="37" t="inlineStr">
-        <is>
-          <t>跨部門溝通協調能力20%</t>
-        </is>
-      </c>
-      <c r="B9" s="38" t="inlineStr">
-        <is>
-          <t>跨部門協辦時，交代是否清楚？（15 分）</t>
-        </is>
-      </c>
-      <c r="C9" s="39" t="inlineStr">
-        <is>
-          <t>✓任務交代內容完整（目的、時程、資料、條件）；對方能一次理解；無需再次確認；無誤會或重工。 (13-15)
-✓大部分交代清楚；偶有細節不足但不影響進度。 (10-12)
-✓資訊常有缺漏；對方需再次詢問後才能理解。(7-9)
-✓說明模糊；資料不足；具有高度誤解風險。 (4-6)
-✓未交代清楚或資訊錯誤；造成流程延誤、返工或責任互推。 (0-3)</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="n"/>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="37" t="n"/>
-      <c r="B10" s="25" t="inlineStr">
-        <is>
-          <t>是否透過正確窗口、不越權、不跳層級？（15 分）</t>
-        </is>
-      </c>
-      <c r="C10" s="26" t="inlineStr">
-        <is>
-          <t>✓所有跨部門需求皆走正確窗口；不直接跳主管下指令；不跨部門亂交辦；資訊一致且透明。 (13-15)
-✓大部分遵守窗口；偶有直接聯繫但不造成誤會。 (10-12)
-✓偶爾忽略窗口或跨職掌；造成他人需再次確認。(7-9)
-✓常態越權、跳流程；造成資訊混亂與作業延誤。 (4-6)
-✓反覆越權、直接指揮他人或跳主管；造成部門衝突或重大錯誤。 (0-3)</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="n"/>
-    </row>
-    <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="40" t="inlineStr">
-        <is>
-          <t>跨部門工作表現30%</t>
-        </is>
-      </c>
-      <c r="B11" s="28" t="inlineStr">
-        <is>
-          <t>*低於等於6分或高於13分，請說明原因：____________________</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="n"/>
-    </row>
-    <row r="12" ht="52" customHeight="1">
-      <c r="B12" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">跨部門回覆速度與協作度（15 分）
-</t>
-        </is>
-      </c>
-      <c r="C12" s="41" t="inlineStr">
-        <is>
-          <t>✓回覆迅速（一般案件 30–60 分鐘內）；主動更新進度；積極協作、不推託。 (13-15)
-✓回覆通常在當天，偶有延遲但會說明。 (10-12)
-✓回覆速度偏慢；常需追催。(7-9)
-✓經常延遲且無說明；造成跨部門作業卡住。 (4-6)
-✓長期不回覆或拒絕協作；造成重大流程中斷。 (0-3)</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="n"/>
-    </row>
-    <row r="13" ht="44.5" customHeight="1">
-      <c r="A13" s="42" t="n"/>
-      <c r="B13" s="43" t="inlineStr">
-        <is>
-          <t>*低於等於6分或高於13分，請說明原因：____________________</t>
-        </is>
-      </c>
-      <c r="C13" s="42" t="n"/>
-      <c r="D13" s="7" t="n"/>
-    </row>
-    <row r="14" ht="70" customHeight="1">
-      <c r="A14" s="37" t="n"/>
-      <c r="B14" s="44" t="inlineStr">
-        <is>
-          <t>遇到問題時，是否會先查制度流程？（15 分）</t>
-        </is>
-      </c>
-      <c r="C14" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">✓遇到問題會先查 SOP、流程、辦法，再提出問題；提問前已掌握背景資訊；80% 以上問題能自行依制度解決 (13-15)
-✓大部分情況會查制度；偶爾先問人，但提問內容完整。 (10-12)
-✓多半直接詢問，僅在提醒下才會查制度。 (7-9)
-✓幾乎不查制度；經常造成他人反覆解釋相同內容。 (4-6)
-✓完全不查制度；反覆詢問相同問題；造成跨部門延誤或錯誤。 (0-3)
-</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="n"/>
-    </row>
-    <row r="15" ht="62.5" customHeight="1">
-      <c r="A15" s="46" t="inlineStr">
-        <is>
-          <t>跨部門工作態度
-35%</t>
-        </is>
-      </c>
-      <c r="B15" s="47" t="inlineStr">
-        <is>
-          <t>*低於等於6分或高於等於13分，請說明原因：_________________________</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="n"/>
-    </row>
-    <row r="16" ht="62.5" customHeight="1">
-      <c r="B16" s="25" t="inlineStr">
-        <is>
-          <t>資料正確性與完整性（20 分）</t>
-        </is>
-      </c>
-      <c r="C16" s="26" t="inlineStr">
-        <is>
-          <t>✓資料一次到位、完整正確；無需補件；不造成延誤；正確率 95% 以上。(16-20)
-✓偶有小錯但能立即補齊；不影響流程；正確率 85–94% (13-15)
-✓常需補件；資料不完整；造成跨部門需再次確認；正確率 70–84%。 (9-12)
-✓經常資料錯誤或缺漏；需主管介入；正確率 50–69%。 (4-8)
-✓錯誤頻繁；資料重大缺漏；造成流程中斷或退件；正確率 &lt;50%。 (0-3)</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="n"/>
-    </row>
-    <row r="17" ht="55" customHeight="1">
-      <c r="B17" s="28" t="inlineStr">
-        <is>
-          <t>*低於等於8分或高於等於16分，請說明原因： _________________________</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="n"/>
-    </row>
-    <row r="18" ht="23.5" customHeight="1">
-      <c r="C18" s="32" t="inlineStr">
-        <is>
-          <t>總分</t>
-        </is>
-      </c>
-      <c r="D18" s="48">
-        <f>SUM(D8:D17)</f>
-        <v/>
-      </c>
-      <c r="AK18" s="49" t="n"/>
-    </row>
-    <row r="19">
-      <c r="D19" s="7">
-        <f>IF(OR(
-  AND(D18&gt;=90, COUNTIF($D$18:$Z$18, "&gt;=90")/COUNTA($D$18:$Z$18)&gt;0.05),
-  AND(D18&gt;=80,D18&lt;=89, (COUNTIF($D$18:$Z$18, "&gt;=80")-COUNTIF($D$18:$Z$18, "&gt;=90"))/COUNTA($D$18:$Z$18)&gt;0.2),
-  AND(D18&gt;=70,D18&lt;=79, (COUNTIF($D$18:$Z$18, "&gt;=70")-COUNTIF($D$18:$Z$18, "&gt;=80"))/COUNTA($D$18:$Z$18)&gt;0.4),
-  AND(D18&gt;=60,D18&lt;=69, (COUNTIF($D$18:$Z$18, "&gt;=60")-COUNTIF($D$18:$Z$18, "&gt;=70"))/COUNTA($D$18:$Z$18)&gt;0.3),
-  AND(D18&lt;=59, COUNTIF($D$18:$Z$18, "&lt;=59")/COUNTA($D$18:$Z$18)&gt;0.05)
-), "⚠ 超標！", "")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="C14:C15"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/eval_output/廠務部_陳家祥_評分表.xlsx
+++ b/eval_output/廠務部_陳家祥_評分表.xlsx
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C5" s="3">
-        <f>COUNTIF(D6:P6,"&lt;&gt;")</f>
+        <f>COUNTIF(D6:D6,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -1064,6 +1064,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="12">
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="A2:I2"/>
